--- a/templates/hanson-half-marathon-beginner-template.xlsx
+++ b/templates/hanson-half-marathon-beginner-template.xlsx
@@ -2671,7 +2671,7 @@
         </is>
       </c>
       <c r="G40" s="15" t="n">
-        <v>8.800000000000001</v>
+        <v>13.6</v>
       </c>
       <c r="H40" s="61" t="n"/>
       <c r="I40" s="123" t="n"/>
@@ -2881,7 +2881,7 @@
         </is>
       </c>
       <c r="G47" s="15" t="n">
-        <v>8.800000000000001</v>
+        <v>12</v>
       </c>
       <c r="H47" s="61" t="n"/>
       <c r="I47" s="123" t="n"/>
@@ -3091,7 +3091,7 @@
         </is>
       </c>
       <c r="G54" s="15" t="n">
-        <v>8.800000000000001</v>
+        <v>11.2</v>
       </c>
       <c r="H54" s="61" t="n"/>
       <c r="I54" s="123" t="n"/>
@@ -3301,7 +3301,7 @@
         </is>
       </c>
       <c r="G61" s="15" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="H61" s="46" t="n"/>
       <c r="I61" s="123" t="n"/>
@@ -3509,7 +3509,7 @@
         </is>
       </c>
       <c r="G68" s="15" t="n">
-        <v>8.800000000000001</v>
+        <v>11.2</v>
       </c>
       <c r="H68" s="61" t="n"/>
       <c r="I68" s="123" t="n"/>
@@ -3705,7 +3705,7 @@
         </is>
       </c>
       <c r="G75" s="15" t="n">
-        <v>16</v>
+        <v>18.4</v>
       </c>
       <c r="H75" s="61" t="n"/>
       <c r="I75" s="123" t="n"/>
@@ -3901,7 +3901,7 @@
         </is>
       </c>
       <c r="G82" s="15" t="n">
-        <v>12</v>
+        <v>15.2</v>
       </c>
       <c r="H82" s="46" t="n"/>
       <c r="I82" s="123" t="n"/>
@@ -4097,7 +4097,7 @@
         </is>
       </c>
       <c r="G89" s="15" t="n">
-        <v>13</v>
+        <v>15.4</v>
       </c>
       <c r="H89" s="46" t="n"/>
       <c r="I89" s="123" t="n"/>
@@ -4293,7 +4293,7 @@
         </is>
       </c>
       <c r="G96" s="15" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="H96" s="46" t="n"/>
       <c r="I96" s="123" t="n"/>
@@ -4489,7 +4489,7 @@
         </is>
       </c>
       <c r="G103" s="15" t="n">
-        <v>13</v>
+        <v>15.4</v>
       </c>
       <c r="H103" s="46" t="n"/>
       <c r="I103" s="123" t="n"/>
@@ -4685,7 +4685,7 @@
         </is>
       </c>
       <c r="G110" s="15" t="n">
-        <v>12</v>
+        <v>15.2</v>
       </c>
       <c r="H110" s="46" t="n"/>
       <c r="I110" s="123" t="n"/>
@@ -4881,7 +4881,7 @@
         </is>
       </c>
       <c r="G117" s="15" t="n">
-        <v>16</v>
+        <v>18.4</v>
       </c>
       <c r="H117" s="46" t="n"/>
       <c r="I117" s="123" t="n"/>
